--- a/attribute_table.xlsx
+++ b/attribute_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Kerjaan\GIS Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B967C47-A2AB-46A2-909E-8984E2C55B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D0611A-705C-4264-9C52-63BF694E7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11470,7 +11470,7 @@
     <t>MULTIPOLYGON (((96.65076546100005 2.124265654000055, 96.61130849700004 2.103955282000072, 96.64937555900008 2.057841928000073, 96.68865581200004 2.090836963000072, 96.65076546100005 2.124265654000055)), ((96.44397284400009 2.331835405000049, 96.49795335900006 2.362722520000034, 96.48678960700005 2.415836045000049, 96.45340580500005 2.476020537000068, 96.40168851300007 2.491025504000049, 96.38478276400008 2.464917830000047, 96.34595389600008 2.546004789000051, 96.27051410600006 2.573748971000043, 96.18787358100008 2.651053542000056, 96.16739643300008 2.636611628000026, 96.09929210800004 2.648667205000038, 96.11381137600006 2.715037084000073, 96.09188742700007 2.748606042000063, 96.02648536900006 2.756550240000024, 95.97563826900006 2.811486057000025, 95.90415866500007 2.823996891000036, 95.87051120300004 2.846468127000037, 95.90472983500007 2.89483781000007, 95.87229778200003 2.913189403000047, 95.76812856800007 2.89716717400006, 95.76749981500006 2.826245633000042, 95.73487222100005 2.831777049000038, 95.69214494500005 2.774035956000034, 95.72623635700006 2.76054283700006, 95.75514998200003 2.700443351000047, 95.81794538800006 2.647672502000034, 95.86313085900008 2.637958729000047, 95.94221079200008 2.57204727900006, 95.97432039500006 2.588661410000043, 96.08024653000007 2.566679538000074, 96.12620842000007 2.522887351000065, 96.16067285800005 2.512057391000042, 96.22809250600005 2.442110755000044, 96.31778222800006 2.415539484000021, 96.31971927600006 2.36189779800003, 96.34457312700005 2.341427228000043, 96.38689060400009 2.349229736000041, 96.44397284400009 2.331835405000049)))</t>
   </si>
   <si>
-    <t>Makassar</t>
+    <t>Kota Makassar</t>
   </si>
 </sst>
 </file>
